--- a/Employee_Reports_wi48/Alen Cherippanat Babu Q0515.xlsx
+++ b/Employee_Reports_wi48/Alen Cherippanat Babu Q0515.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-354</v>
+        <v>-357</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
